--- a/data/google_news_dedup_27_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_27_0426_UTC_past2d.xlsx
@@ -480,32 +480,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brand Retail Crime</t>
+          <t>BV Value Retail Crime (fallback)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "Louis Vuitton" OR "Burberry" OR "Prada" OR "Nike" OR "Canada Goose" OR "Hugo Boss" OR "Moncler" OR "Saint Laurent" OR "Loro Piana" OR "Lacoste" OR "Versace" OR "Jimmy Choo" OR "Michael Kors" OR "Missoni" OR "Kiton" OR "Aquazzura" OR "Tumi" OR "Rolex" OR "Cartier" OR "Chanel") AND ("theft" OR "stolen" OR "shoplifting" OR "smash and grab" OR "ram raid" OR "robbery" OR "burglary" OR "heist" OR "pickpocket" OR "organised crime" OR "gang" OR "arrest" OR "convicted" OR "sentenced" OR "counterfeit" OR "fake" OR "money laundering") AND -sport AND -"watch review" AND -"price drop"</t>
+          <t>("Bicester Village")</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anta: The Chinese sports brand taking on Nike and Adidas - BBC</t>
+          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anta: The Chinese sports brand taking on Nike and Adidas - BBC</t>
+          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:09:42 GMT</t>
+          <t>Mon, 27 Apr 2026 08:11:26 GMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE43MVFBLUtjcGZwck5Gbkw2UFQtc1JtVUNmQ0FHU0NqUzdhRklTN25DaDM1X3JUbVhVVlo4d0xsSVRBM0JXTzRCVmRUYWRPYU9DSkt2YlM5YTAzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNbWxnaDNwV3FOSGg3YzNJcjNSVDVGWmFPSE9pSXMwOXoyZUJBajNtUFJLNkl3Wm5wZXNlNGlxeW9MNlJqZ19ZdWdaNDRtT3J3ZTR0YTFwZml3UHhGS1FkUHdUMHMzbV9uRWxtcUVpenk4LVpsQ0hlRkl3aUdZV29fZlRXVmMxVjRiNzQzVjdNMzRHbUlITU4wWXFOUDJtSnRFbGEyZmNBbS1vNkI3Z2gyXzlPM3JfQ0F4eU5ON3FnbWZ5Vml0WElpeHhnRDdwOGtDRkxyZGVrS0Ywcl9ldVVJTDAzUC16UnNmWFB1X3Y4MkR6NUJRSmprNnNmMXhwbXpUaW1JcWlR?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46139.29840277778</v>
+        <v>46139.34127314815</v>
       </c>
     </row>
     <row r="3">
@@ -710,22 +710,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Teamsters, drivers protest at Amazon’s DBK4 facility in Maspeth over third-party delivery model - qns.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Teamsters, drivers protest at Amazon’s DBK4 facility in Maspeth over third-party delivery model - qns.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:02:30 GMT</t>
+          <t>Mon, 27 Apr 2026 13:00:53 GMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOWV9uZGI0eDFqeUlFajVoeHB4X290MFBHamVkX053Wml2b1BPNG9aaTdtTEpEZTN1N3JrSUNfT2lzbC1sTGgxQV9oRDdWTWRYOE1UamwxaExiX0JaTzNzbnZtajU1Y3R4U0YwRUlJSHJfYl9ScEkyNC1xMFN3dk5hTGVTcTRlbzB5YVVaa3djZWFuUVhxMUZ6bmZaWnlhZEo0V1ZvMDVvUEphUFFWTF9wX3BXOUJVRk5BUlc4T2RyNlNFMVh2bGRFUTNFRdIB2AFBVV95cUxQU2Z3dlZIcG15TGhrd0pzNEVFVlhvU2pyWGREb0lFWlVONV9sN0gwcGJDeUhfbWZ4TkdQdTJVZ1dVYzlRMjFraVpORVdmZnBWOUJibDVrRlVGRGVTRTRSRXR0SG1TS1JneUFCVGZ5ZUVTejhydFdRdWRhNEJjdlFFVF9rblFManpiWTZBY2MwcUY2Ym1hS3ZmM1FPUjJCQ1ZyeHYzQUxXMm5HUXJacUd4czF1WUJEeVJXdGRsVkRrNlpWaGVhZjdzSWludGVCS0xmcG1zSE9XZU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE80ekZNMkhud0lzSkJJTk93OC15TDJqT1pkTjBidk9yU3JLRUdvRW1jay1RXzk5Q3QyUkhPR3NzMnhrdklzaFJPajJLS2tmMWxIUFdDY0pGbFFINm5YMV9MaE1mRmtabnh5Tl9NMDlwZlM?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46139.29340277778</v>
+        <v>46139.5422800926</v>
       </c>
     </row>
     <row r="7">
@@ -765,22 +765,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teamsters, drivers protest at Amazon’s DBK4 facility in Maspeth over third-party delivery model - qns.com</t>
+          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Teamsters, drivers protest at Amazon’s DBK4 facility in Maspeth over third-party delivery model - qns.com</t>
+          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 13:00:53 GMT</t>
+          <t>Mon, 27 Apr 2026 13:39:23 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE80ekZNMkhud0lzSkJJTk93OC15TDJqT1pkTjBidk9yU3JLRUdvRW1jay1RXzk5Q3QyUkhPR3NzMnhrdklzaFJPajJLS2tmMWxIUFdDY0pGbFFINm5YMV9MaE1mRmtabnh5Tl9NMDlwZlM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinANBVV95cUxOZktuMXg0VGFoYnY1U2FoM1hRbXNxcEg5ZEM4ekhObFVZVFlXTDJVLWo0eGhiQWpaUHhrNks3eTZMdWZRa2lOYm96LTdPelJjMERsMm9DU2ZBQkdlWWlXMlZFUHVreWNmRm1Ea29DYTFIc1o1MHQtSHlUSGt0MFN3NDBIX1hWM1pHRDNlUHdOM0NMd2xrN3V5SS1FLWNkMzZmT0VmcTJfR3JoQ0lWYmpOQ05DS05iODV5dnU3TmFKVmVKRWZGTmtVSkxwMXMzMXNaNjl3eWRrY2Rqb0J1cUlzM05wR3BPVkVMSnJRS2VZaEdpYmRUU0NYeFZXSDRwYlJ3X1N1WmVsTkJIYmN6eElJRUpCT3lZUVFucHN2TGhnV3FRRXduVWhSMER2bUFhVXN3NjNPZkI3bmFmUmlaMWM4cXBoMWdHVmQtYjJJeUpFQ0FFWVM2eHhWTHRSQWVCOTBEem5jWnNKb3ItVXQ1ZjZWejE4QmZacHpKY3o5bnhLTmJRZEsxR0N4WnZ3X2JSRVlRajZvRzBYdFppRE1Z?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46139.5422800926</v>
+        <v>46139.56901620371</v>
       </c>
     </row>
     <row r="8">
@@ -820,22 +820,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amazon’s first delivery station in Bryan holds a ribbon-cutting - MSN</t>
+          <t>Amazon Now to reach 100 cities with 1,000 plus centres in Rs 2,800 crore push - Indian Television Dot Com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Amazon’s first delivery station in Bryan holds a ribbon-cutting - MSN</t>
+          <t>Amazon Now to reach 100 cities with 1,000 plus centres in Rs 2,800 crore push - Indian Television Dot Com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:38:58 GMT</t>
+          <t>Mon, 27 Apr 2026 09:15:35 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVmtwNW9vSlhUandNVWtna3VxbWctczNuX3NneFhpbTdMNlhFb0RfenhtZEozclI1dy1hVDU3aFQ5RkxUbkF2ZHRETGNXZ3Q1VHNQRU5NZ3MxVXhBaDJBdURvam81U29IZXlwNGNaaTFfdktnVjczZnFxVjI4ZDNmQVlOSXlFbk9NUFlwWlluWHRteWtsWWNZLXRvWW5xQUZGcnBSaGo2YjhZMFIyU0R2aG1TZHhneXRH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPZW15RWdFc01KUWtqNmlNdkoyRWdVeFdQQ24xVGg2LTIxeFZmRkhmbkZEV29JZUcxR0FEc20yTHdxQUFVc0I5eHJyQzE2WDR1TXdZczB2T2x2bVRaRDhpQ01nUlJWdGluV2I1ZnZfMjBhWDM0NG5kWTNiQkZnYmxia0ZMblU1NUprMFRUTm9PSkJFSFAxWGZjNVU0NHlMYjdkVlFfWG56eTJQMlA4VFE?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46139.31872685185</v>
+        <v>46139.38582175926</v>
       </c>
     </row>
     <row r="9">
@@ -875,22 +875,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The delivery speed wars are heating up as Amazon rolls out 1-hour delivery - MSN</t>
+          <t>Amazon’s first delivery station in Bryan holds a ribbon-cutting - MSN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The delivery speed wars are heating up as Amazon rolls out 1-hour delivery - MSN</t>
+          <t>Amazon’s first delivery station in Bryan holds a ribbon-cutting - MSN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:01:01 GMT</t>
+          <t>Mon, 27 Apr 2026 10:05:02 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwNBVV95cUxNenRYdkNOSk5KQmFUVzBCcVJ2V0RTeXU0S25tVk9XOUlXNHlKUXBTbW9GVm9uVVpxYklsSVBUdk85NVVvRGRoSU9ScUhyaVlyRm1Pc252Rm9ETWZqZWlvMU54c0w5TExGdm9TZm1lY1dwd0Q4WEw1clBpcmk3aXpSWnFZMl94dlp3TnZTRTI4ZDBDbEJuNGdDeFg5U296SzhrelFsem1KcGlxam4wVlA4WjQ0TXRCNmlwUjhXa0g1d3B6THczbzBsVG1pX2NPT1JscTlKOFpqODVsQzIweWdhby1TMU1RT3FGVFRmcVYyUzJPUDIyaUZUOUJ0Z2pBUnJpakp2TktzcVVVNEZ3d2VnOUhTS1F0MG9PWjliTWxTRFh6T2h1TmdLZTdmV1VuSnptTlBjYXhfY2VXU2Y2WlZ2aWJJdHB1UnBXSDFTSGM3VUR4VThKZU9GejhNU3AtREU3RHBDQnAwQ2sxQjlHaDJ0NU92dzlpVXljcFkyUk1taFhzSGt4OU0zMDVDM3pXZ2M4aEhqelE2Uy0tV21WQTg0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AJBVV95cUxOWFhxOFc3R05ObEh5NzVZajg2ZHdSbno0blR2cEwtZ3NYSnFaOTlBaDYzejMyaHVGQTZzR1Fpb3h4SGx0QTI0cy02SG1PTGc2azBxMGZPMk1zdGVUVGFPTEItZGtVMzVvMTA4YlNKOEUzMjNaMGtraGJ6Mk83dnpRVERwNmRUc3MtZ0dSaFAwSmNNbnZPWWVfNkxTd2FVbVZDdkRYdjQ0YjhReHZYcHBUMVUwVWxZV1lBeDZOcmFwZUxxQUNWUkNRRG94Q3RIYlIzTlpadEpLZWphQml1WWJNZmh0bnVwVWliekNjOUdDeWk4ZGNaRTZUOUpzckVBUkN0VXZrelJINVo2UEtXMDd2dXRZZTdubThfUHd0Y29icEdzSmFnYWJaclVveFkzT285S3JPbmRyNzlFMGYtYW5IT3RQWGUxQ29BTUtMOVduamkycUhMM2MybUVGQW5WbklPVWlvVC02OGVOYjVp?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46139.29237268519</v>
+        <v>46139.42016203704</v>
       </c>
     </row>
     <row r="10">
@@ -985,22 +985,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verdachte (34) steekpartij in Antwerpen aangehouden voor poging doodslag: slachtoffer (31) niet langer in levensgevaar | Foto - pzc.nl</t>
+          <t>Hardhandige arrestatie van minderjarige drugsverdachte in Antwerpen roept vragen op: “Wordt intern geëvalueerd” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Suspect (34) stabbing in Antwerp arrested for attempted manslaughter: victim (31) no longer in danger of death | Photo - pzc.nl</t>
+          <t>Heavy-handed arrest of underage drug suspect in Antwerp raises questions: “Is being evaluated internally” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 08:14:13 GMT</t>
+          <t>Mon, 27 Apr 2026 14:54:26 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOaktvTTdUYWptSmFLV1VObUlXbUtyNjJQT3Y2eFgtNll2NC0zQXhYVHlISDdXclhMNnJuWmpBbllQOUE0dWk2eW1sQTVuRFJfRUo1VmdXUkhDX3BaRWN5V0JtMm1lNWlLUHdNejlTeU9HWWIxWW4wdElxWXcyclVCSEY0aU44LTh6TUkwdHI1WktiV0hKQVhzb2hrZTU3cFdiT2NZS05lNkh5ekxPZWhkbHR0WGZWOVc3eTY2VDBCZXQxd3pfQ3otb1Ffc2VmUHNGb3ZZdlpnRmxaeXBRUER4d1B3bEcxMUY0TXE0Q3VnZUFpbkdadWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQV19GMG9abjJwMENVVFotR0xOd1NTSDhpRHhCMUhlOWJjVU9pd1NXZEdJc0d5U0ZMdHhSQVVKcko3bWZNbi1UNFZtZUo5NTRBckJ6N0Jua2JwQlg0dHZINGVsNmNQQUNReVY5X25DOWhTYWtENXkxNDNZaU9VUHl2UE1VRjVVMFNaMHJkMWR2SEhVTUo2Y25oRUhZblZENzZxM282SFBHTVduX09TNng0QXZHYWR4bEgyQnRVbWJSN1RTUE8zaFNJZjlieEhwLTQwNkxzdDQwemMtOVlVS0FFbzFfcThkdXRaam9jeU1PY3U5Zw?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46139.34320601852</v>
+        <v>46139.62113425926</v>
       </c>
     </row>
     <row r="12">
@@ -1040,22 +1040,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Man (34) in levensgevaar na steekpartij in centrum van Merksplas: verdachte opgepakt - Nieuwsblad</t>
+          <t>Verdachte (34) steekpartij in Antwerpen aangehouden voor poging doodslag: slachtoffer (31) niet langer in levensgevaar | Foto - pzc.nl</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Man (34) in danger of life after stabbing in the center of Merksplas: suspect arrested - Nieuwsblad</t>
+          <t>Suspect (34) stabbing in Antwerp arrested for attempted manslaughter: victim (31) no longer in danger of death | Photo - pzc.nl</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 09:59:04 GMT</t>
+          <t>Mon, 27 Apr 2026 08:14:13 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOWFhDMU40LWNiMVlJWTI3QXRuUXhBNjJFaF9EV1B2QktVSkNaOF9WeUFXdE5xOHllRXh1dzRlSmpMZlQ5aVJ2dU91Mm5vN1NoMllCeTA0ZW00amV2UkYzNjRJMHZqUUI5UUNkMkpGZjk1cjE3YWcwekFWbDdSMjdxYnFZbjRrY2tnbEtBRHhGZEh0aUpPTXhfWTZuQTZ1ak1mMHN1ZWo1dUk4cHBtM1dfa0drRmdPaDdDaV9BM1BEQzZWZmRJT29mb0dCS1ZfT2dRdTRWa1RSTGNoTzhma1F2SGxmOXZrczVad0tj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOaktvTTdUYWptSmFLV1VObUlXbUtyNjJQT3Y2eFgtNll2NC0zQXhYVHlISDdXclhMNnJuWmpBbllQOUE0dWk2eW1sQTVuRFJfRUo1VmdXUkhDX3BaRWN5V0JtMm1lNWlLUHdNejlTeU9HWWIxWW4wdElxWXcyclVCSEY0aU44LTh6TUkwdHI1WktiV0hKQVhzb2hrZTU3cFdiT2NZS05lNkh5ekxPZWhkbHR0WGZWOVc3eTY2VDBCZXQxd3pfQ3otb1Ffc2VmUHNGb3ZZdlpnRmxaeXBRUER4d1B3bEcxMUY0TXE0Q3VnZUFpbkdadWc?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46139.41601851852</v>
+        <v>46139.34320601852</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Politie pakt verdachten van reeks inbraken op: “Observatie van hun auto leidde tot arrestatie” - HLN</t>
+          <t>Man levensgevaarlijk gewond na steekpartij in Merksplas - rtv.be</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Police arrest suspects in series of burglaries: “Observation of their car led to arrest” - HLN</t>
+          <t>Man seriously injured after stabbing in Merksplas - rtv.be</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 09:10:32 GMT</t>
+          <t>Mon, 27 Apr 2026 09:03:31 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOaklzMVd2OFRwazRpRm9tdVBCbnBvTVQtUndzNy1TeEMydm83U2ZDZTA4Ny11ZjNHcGoyMkdzbDFXNUJZSnpXWWxWZ2piX2Fka09tRU05Vlg5VlVzTlhlaFFXWVVrRUVaZmJvREFBeDNHSzZfc2x0OEJiOExGYXltbWktc1lzbjExXzhXOHB6VlZhdVd3aF9TYVJ6Z0dlc291Ull0TnQ1c00zb1RUMHBnN0RPVjlwSlR5djJzV3Ztd0ZPTkRxNXMzem11b3RySFhiZEk2WXptUlZxSWMtQk0wNlQ0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNUzFKaGloSE5Yb1A3UWxVaktZN3ZqbGxoZFNPV0JWM2JGQ21BS09JU3dqbU5LRmRoTVdOdFk4WVB6aElVQUd0VHZGQjRDWDlobTl1cHI3Vl9MLVVqa1JwV0xQeHYycElJaHVhcFltY21ONTZZX3V6c2pBMk9PSEVtclBWV25ZcHlNTjJZN01qRG9PZWFoRjMwYw?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46139.38231481481</v>
+        <v>46139.37744212963</v>
       </c>
     </row>
     <row r="14">
@@ -1205,22 +1205,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Speurders op assisenproces over roofmoord op Johanna: “Er is meer dan één mes gebruikt” - Nieuwsblad</t>
+          <t>Politie pakt verdachten van reeks inbraken op: “Observatie van hun wagen leidde tot arrestatie” - HLN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Detectives at assize trial about the robbery murder of Johanna: “More than one knife was used” - Nieuwsblad</t>
+          <t>Police arrest suspects in series of burglaries: “Observation of their car led to arrest” - HLN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 11:28:00 GMT</t>
+          <t>Mon, 27 Apr 2026 14:54:43 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNWmhpdlRSVENiMHl5cFRaejF6aWtjdkxpZXNYM1I3RHc0RW1hcTcxMUQwU29ZaUhxbFB2alY4RzJ2NWhMX3ljbEwzc2ozVWNKZGN4X05ZS3ZuS3NlVmt4bmdCTU1xX3JvTmZ0R0xTSTNwMmg5VG1jODZab2hLT0w3YUlhbHlveGdBYXdCUDdGZTg4S043Q0xfUmJ6eWJfUWZrbXo3VEVtUDNWclItZEtIZ3JFNHFGYnJObWVYS2hqam56VEJGaGJwQnJmNVA1ejB6ZFJtc2I2S3VERkJCbEZHY3MxalR4S295dm4xc0pSdEhyZ3BrV1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQRElhVGxSNHMzVXRSa0Q4X180SHBycDdWM2RJNGR2V1hCWjZVZE9qdHgtc3ZETERCelRzclVoc0xRUGZaT0x6ODlXVXNmcGtGZG8zUGJMMHRvMUNTM3JRLWNkUVRxOUNWWDlFX3FYc2U1c1ViYXRncmZDWTVOcU9vMUtJY2x4cmczNlFsem94QjZLOE83dkNfSDYya3JMTUcwU09CbG5tN2RmOXZQYWVLWU9LVnl1SkNPUC1nZGJyZFdPUVM3dXI0anUxOU5qaHhmVXZscWMzQUJaamZJNEh6NEtkYWY?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46139.47777777778</v>
+        <v>46139.62133101852</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Albanese man aan België overgeleverd voor betrokkenheid bij cannabisplantages - Nieuwsblad</t>
+          <t>8.000 bezoekers voor Brusselse nocturnes - Nieuwsblad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Albanian man extradited to Belgium for involvement in cannabis plantations - Nieuwsblad</t>
+          <t>8,000 visitors for Brussels nocturnes - Nieuwsblad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 13:41:40 GMT</t>
+          <t>Mon, 27 Apr 2026 15:02:30 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOOTlGS05EdjEzZ0N5ck9mcDFSYTZ5TXJBRU9TTkl6NW5SeUVSYnNMcVhPSUdna2ZLclRmZ1E1bXFOUHVneE14N2t4Ry1aMWsxcWlTOEZyUWdPNk1sclNoWEpnM1RyUmdrOThFOG1lOFVZQ0FsZlh4RWpNOWlPZkp5THg5VGhYWkVWLU92STg0dFZOclRHWmZaMUYxNXJ1VGhvU1ZSQk9DeTJNTjFjOUdoQXd3Qm5yWElsUWV1blhwZkpSdXcyT0ZmSkI2bGNrOG85ejhQMW1mb0hFUkRHdEl2T2NoXzVwbnJPdVpBNGJpRW9RQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQaGZaZmhaaURSTExRX1pkRUQ2azVXSjMxMDB1SWJZdmt4bXNLY2QzbmM3d080TXR3WEphTHM3V19pT2REeHNTMXNqY2Y2aXRELTFSa3ZtV2dheXhJdWNTZUZWa2ZLTjc2MFFGVWpvbWZSMDRhV1hxUVVaLTFFRV9yNTdYWk5xdzI2STYwUG5TR2tpb1c4T1BvM0NwS2pESXhDZEVVOXZB?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46139.57060185185</v>
+        <v>46139.62673611111</v>
       </c>
     </row>
     <row r="17">
@@ -1315,22 +1315,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remi (82) en Monique (80) zijn diamanten echtpaar - Nieuwsblad</t>
+          <t>Speurders op assisenproces over roofmoord op Johanna: “Er is meer dan één mes gebruikt” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Remi (82) and Monique (80) are a diamond couple - Nieuwsblad</t>
+          <t>Detectives at assize trial about the robbery murder of Johanna: “More than one knife was used” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 09:33:03 GMT</t>
+          <t>Mon, 27 Apr 2026 11:28:00 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPRlVzVEhaVlNwVzFxR0JtdDg1ZFVxdVc2QmNGLUsxTlZXUXVpN3l6M0hoRll6VFA4YWJFU3dldzd6cDV4MU1RaHBqZVR3dUFzZDhBcDZPMUZXQnNlRUMyRzlMcEZBMWk0VFc1eFVUbUpFeW55UUZnWlVvcGV6MnVGcENTSmJmOTh3bW9EMnlKcW9Nb2xyQ0tsYldYTDVWMTZsT2lOZ3FkTkZ1cERTcWR6SWd1dTRJal9VTVdjTEh0Y0loV2M0SUh0eXFLa2Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNWmhpdlRSVENiMHl5cFRaejF6aWtjdkxpZXNYM1I3RHc0RW1hcTcxMUQwU29ZaUhxbFB2alY4RzJ2NWhMX3ljbEwzc2ozVWNKZGN4X05ZS3ZuS3NlVmt4bmdCTU1xX3JvTmZ0R0xTSTNwMmg5VG1jODZab2hLT0w3YUlhbHlveGdBYXdCUDdGZTg4S043Q0xfUmJ6eWJfUWZrbXo3VEVtUDNWclItZEtIZ3JFNHFGYnJObWVYS2hqam56VEJGaGJwQnJmNVA1ejB6ZFJtc2I2S3VERkJCbEZHY3MxalR4S295dm4xc0pSdEhyZ3BrV1E?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46139.39795138889</v>
+        <v>46139.47777777778</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Werfzone palmt grootste deel Gasthuisstraat in - Nieuwsblad</t>
+          <t>Albanese man aan België overgeleverd voor betrokkenheid bij cannabisplantages - Nieuwsblad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Construction zone takes over most of Gasthuisstraat - Nieuwsblad</t>
+          <t>Albanian man extradited to Belgium for involvement in cannabis plantations - Nieuwsblad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 09:37:13 GMT</t>
+          <t>Mon, 27 Apr 2026 13:41:40 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVlExOHU1eG1PakNGZUxaOHJaYll1bzR3VVJxcUJ4RUdKQkh2RVNkR1pJVGd2M2ZxSFNJUWFMTGJROVZMM0t6akZLR2g4UUEzejc1UjNTSk5ITE5UT0JBMTBoMnNMY0pXaW5YeERZZ2NwWkpfbzB2QVU0bHBGTmJNNTFpNm9KTVZ3VUNFVWxsQXEtaFZ2Q1BwVWVwaWVZTDh2SDdTbEMzSGNENFg1c3dnbWliNEx3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOOTlGS05EdjEzZ0N5ck9mcDFSYTZ5TXJBRU9TTkl6NW5SeUVSYnNMcVhPSUdna2ZLclRmZ1E1bXFOUHVneE14N2t4Ry1aMWsxcWlTOEZyUWdPNk1sclNoWEpnM1RyUmdrOThFOG1lOFVZQ0FsZlh4RWpNOWlPZkp5THg5VGhYWkVWLU92STg0dFZOclRHWmZaMUYxNXJ1VGhvU1ZSQk9DeTJNTjFjOUdoQXd3Qm5yWElsUWV1blhwZkpSdXcyT0ZmSkI2bGNrOG85ejhQMW1mb0hFUkRHdEl2T2NoXzVwbnJPdVpBNGJpRW9RQQ?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,38 +1409,38 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46139.40084490741</v>
+        <v>46139.57060185185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mexican president calls for tighter World Cup security following deadly tourist shooting - Travel Tomorrow</t>
+          <t>Remi (82) en Monique (80) zijn diamanten echtpaar - Nieuwsblad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mexican president calls for tighter World Cup security following deadly tourist shooting - Travel Tomorrow</t>
+          <t>Remi (82) and Monique (80) are a diamond couple - Nieuwsblad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 08:06:50 GMT</t>
+          <t>Mon, 27 Apr 2026 09:33:03 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNV18zSVFjdk1IUlZoSHdnSGwxam5jVEVWNDREenl1SlczYnkzZ2Y1ME01MnZldWtwV0N0dTVWWjBIR0FCaVRCUi1fYk4wMXFKdkRWWG4zWFRmcC1MZS10R0k3TC13Nk4wS3ZPNnVhM3RIN2NPTld6ajRLWEhWb3ZxVGNsNTZ1U19hLTdTbEdvaXlyeGlnMjZGODZGbV9vNzVnb0pqQkEwNGk2cFZyN01SSGNvV2h1LUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPRlVzVEhaVlNwVzFxR0JtdDg1ZFVxdVc2QmNGLUsxTlZXUXVpN3l6M0hoRll6VFA4YWJFU3dldzd6cDV4MU1RaHBqZVR3dUFzZDhBcDZPMUZXQnNlRUMyRzlMcEZBMWk0VFc1eFVUbUpFeW55UUZnWlVvcGV6MnVGcENTSmJmOTh3bW9EMnlKcW9Nb2xyQ0tsYldYTDVWMTZsT2lOZ3FkTkZ1cERTcWR6SWd1dTRJal9VTVdjTEh0Y0loV2M0SUh0eXFLa2Y?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46139.3380787037</v>
+        <v>46139.39795138889</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dinesh Trivedi appointed India’s envoy to Bangladesh amid push to reset ties - Firstpost</t>
+          <t>Werfzone palmt grootste deel Gasthuisstraat in - Nieuwsblad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dinesh Trivedi appointed India’s envoy to Bangladesh amid push to reset ties - Firstpost</t>
+          <t>Construction zone takes over most of Gasthuisstraat - Nieuwsblad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 10:50:19 GMT</t>
+          <t>Mon, 27 Apr 2026 09:37:13 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNM1RoaVZGS3ZWbnVXbHJtZVZ3NXQ4UUFGekhka3BPN1kxZHpuSXg1dExOZGFOZklRVzFPemlCRmhXNVVpZlJ0S3lDUXNMelZ6TmFORW8tOWlQWDRrcnFjMXdhYmJ5VXA5bWtHUjZWYlNFWXNNVUdEa1IzdXowalE4eEoyNDVNUVJOaS11d0lZX0hjeGZEaWRETVhBMkRjWjhZU1NVVE9SenRYdnVNc3gwUVlqZUJid2FaVC1meWl30gHDAUFVX3lxTE9qaHJlcGFMamE4bjZhZ0RqTXJxZ2diM2E0X1puMWwxLW9YTkZTaEtUR2lFQjRGa3c1dmV6MGlXaGJnY3ZNYnluaENpX3dFOWVrMzgtOVNnOTB6TzJEYVJuVEVWbTVDR0VuU0Jwd1o1NThPbVZ0Z3RmeVh5c3NCdkYwQmpJbkxzVWxrWVpDQmQ4NHdweWFWYUZfN0NGWkVSTm9RcXJTMEUtWW5jM0U4dDJaZ3UxTUhsdkppdWRCQ3NSVDBOUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVlExOHU1eG1PakNGZUxaOHJaYll1bzR3VVJxcUJ4RUdKQkh2RVNkR1pJVGd2M2ZxSFNJUWFMTGJROVZMM0t6akZLR2g4UUEzejc1UjNTSk5ITE5UT0JBMTBoMnNMY0pXaW5YeERZZ2NwWkpfbzB2QVU0bHBGTmJNNTFpNm9KTVZ3VUNFVWxsQXEtaFZ2Q1BwVWVwaWVZTDh2SDdTbEMzSGNENFg1c3dnbWliNEx3UQ?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1515,11 +1515,11 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46139.4516087963</v>
+        <v>46139.40084490741</v>
       </c>
     </row>
     <row r="21">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Still shaken: Flyer posts video of explosion outside plane window - MSN</t>
+          <t>New aircraft design transforms most dreaded seat into a semi-private retreat - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Still shaken: Flyer posts video of explosion outside plane window - MSN</t>
+          <t>New aircraft design transforms most dreaded seat into a semi-private retreat - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 10:13:25 GMT</t>
+          <t>Mon, 27 Apr 2026 13:17:38 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wJBVV95cUxPMjRHamNUVzFiV2o5Q2NmS0d3a1MzRGJmSmNLUEY0Z1RvTG9qWjZUaGdJTm1PS2czNzAzT2NiaTA3aXgtc1RkOHFFb0RQT3N6SEFoN1ozTWZSM25ob3lwWVVDN2JzMFBRUDhEMFplT3FNZ3E4VEZsd1pQck9ZTlA1UExDYnNaOHBuZmpKZjY2RDJob193anpEVnJKTDg2VFlMVnBfS2ktMHhrS1pLTmk5Y2dwbTdaZ21wMVJWV1llNzJaLXlOelpDVUw1R2FFM1JiNmFyXzNERE9HZ3QzbGxUSzRhVEpOaDRoOXdnODRQWWZEcVhuT3pKcVhQck0zRUJJTkNrdVNicm51OWh0Y3Y1ZG55clVfQVptSzI5akkzSEV3SGpOWWpLcG1hbmdqRnBCYXFDNGtERVJ2ekp2Z2I5TVFGdDlIU3JjdzREOGt6OVNRVkVVMEJXSjl1S2h3MVlPLWJWUWtNSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPSE9melI1U1BSa0VXZWdXRldFb2dJWGQzaEk4M2VNMnljQ3dVZkVOOV9wWnl5X1RGSzc5c1gyYTJ0R2ZoTnBDMl9WN3hyWXgxYmhpVXlwbHJmcXlRdTVDWnRQTndQQ2trMU1TazB0NUFEQXpqWE9QbGxuYjZxY0tTMzROYzUxWWtZMmdBTzhDWGpreExTaHJ5YnpUV1lqbUtDQjFFYTJ5OA?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46139.4259837963</v>
+        <v>46139.55391203704</v>
       </c>
     </row>
     <row r="22">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New aircraft design transforms most dreaded seat into a semi-private retreat - Travel Tomorrow</t>
+          <t>Dinesh Trivedi appointed India’s envoy to Bangladesh amid push to reset ties - Firstpost</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>New aircraft design transforms most dreaded seat into a semi-private retreat - Travel Tomorrow</t>
+          <t>Dinesh Trivedi appointed India’s envoy to Bangladesh amid push to reset ties - Firstpost</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 13:17:38 GMT</t>
+          <t>Mon, 27 Apr 2026 10:50:19 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPSE9melI1U1BSa0VXZWdXRldFb2dJWGQzaEk4M2VNMnljQ3dVZkVOOV9wWnl5X1RGSzc5c1gyYTJ0R2ZoTnBDMl9WN3hyWXgxYmhpVXlwbHJmcXlRdTVDWnRQTndQQ2trMU1TazB0NUFEQXpqWE9QbGxuYjZxY0tTMzROYzUxWWtZMmdBTzhDWGpreExTaHJ5YnpUV1lqbUtDQjFFYTJ5OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNM1RoaVZGS3ZWbnVXbHJtZVZ3NXQ4UUFGekhka3BPN1kxZHpuSXg1dExOZGFOZklRVzFPemlCRmhXNVVpZlJ0S3lDUXNMelZ6TmFORW8tOWlQWDRrcnFjMXdhYmJ5VXA5bWtHUjZWYlNFWXNNVUdEa1IzdXowalE4eEoyNDVNUVJOaS11d0lZX0hjeGZEaWRETVhBMkRjWjhZU1NVVE9SenRYdnVNc3gwUVlqZUJid2FaVC1meWl30gHDAUFVX3lxTE9qaHJlcGFMamE4bjZhZ0RqTXJxZ2diM2E0X1puMWwxLW9YTkZTaEtUR2lFQjRGa3c1dmV6MGlXaGJnY3ZNYnluaENpX3dFOWVrMzgtOVNnOTB6TzJEYVJuVEVWbTVDR0VuU0Jwd1o1NThPbVZ0Z3RmeVh5c3NCdkYwQmpJbkxzVWxrWVpDQmQ4NHdweWFWYUZfN0NGWkVSTm9RcXJTMEUtWW5jM0U4dDJaZ3UxTUhsdkppdWRCQ3NSVDBOUQ?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46139.55391203704</v>
+        <v>46139.4516087963</v>
       </c>
     </row>
     <row r="23">
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>European travel demand hits highest level since 2020, but 90% stay within Europe - Travel Tomorrow</t>
+          <t>Still shaken: Flyer posts video of explosion outside plane window - MSN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>European travel demand hits highest level since 2020, but 90% stay within Europe - Travel Tomorrow</t>
+          <t>Still shaken: Flyer posts video of explosion outside plane window - MSN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 11:12:15 GMT</t>
+          <t>Mon, 27 Apr 2026 10:13:25 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNWTN5WmZSR1dkaUVjVTBWRlFrbXFHNjAtdnAxWUNoRjVWM3B5M0Z0R2stSk83UnBRU2FJWUF2cF9uWXZMekcwb21LTFBNTzJLR0lNMDlBdFg2R2I4YmJyamtOSGxTcTFFeGhNcUdVT3FYRENCM2ROVmFOVFpuQUZJQUM1V0wzWUl6LWVfS0xkR0haU3Z2aV85cnRCOWpmeHdxZ2JGZUVsbUMtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wJBVV95cUxPMjRHamNUVzFiV2o5Q2NmS0d3a1MzRGJmSmNLUEY0Z1RvTG9qWjZUaGdJTm1PS2czNzAzT2NiaTA3aXgtc1RkOHFFb0RQT3N6SEFoN1ozTWZSM25ob3lwWVVDN2JzMFBRUDhEMFplT3FNZ3E4VEZsd1pQck9ZTlA1UExDYnNaOHBuZmpKZjY2RDJob193anpEVnJKTDg2VFlMVnBfS2ktMHhrS1pLTmk5Y2dwbTdaZ21wMVJWV1llNzJaLXlOelpDVUw1R2FFM1JiNmFyXzNERE9HZ3QzbGxUSzRhVEpOaDRoOXdnODRQWWZEcVhuT3pKcVhQck0zRUJJTkNrdVNicm51OWh0Y3Y1ZG55clVfQVptSzI5akkzSEV3SGpOWWpLcG1hbmdqRnBCYXFDNGtERVJ2ekp2Z2I5TVFGdDlIU3JjdzREOGt6OVNRVkVVMEJXSjl1S2h3MVlPLWJWUWtNSQ?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46139.46684027778</v>
+        <v>46139.4259837963</v>
       </c>
     </row>
     <row r="24">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Outdated rail systems make European train travel harder than flying - Travel Tomorrow</t>
+          <t>Mexican president calls for tighter World Cup security following deadly tourist shooting - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Outdated rail systems make European train travel harder than flying - Travel Tomorrow</t>
+          <t>Mexican president calls for tighter World Cup security following deadly tourist shooting - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 11:37:22 GMT</t>
+          <t>Mon, 27 Apr 2026 13:17:38 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNNHZoc1NHNHBPeDRPRm1GY1JkRE5zWWRneXJTUkhKWHRMOUdJZlRJNFJTVF9mOXZIN2ZhNk9lWFljUUM0UVpxZ3FxOWIwTGxtSUlaWm1tVk9TckNFcWRJdG9YVE5CRUhRaGJka2h5RERzdUNxcW5RSU5kSDhzU3JleENLY2d6cE5EVUhLRC1SYUhYNjFQOHpVNDVLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNV18zSVFjdk1IUlZoSHdnSGwxam5jVEVWNDREenl1SlczYnkzZ2Y1ME01MnZldWtwV0N0dTVWWjBIR0FCaVRCUi1fYk4wMXFKdkRWWG4zWFRmcC1MZS10R0k3TC13Nk4wS3ZPNnVhM3RIN2NPTld6ajRLWEhWb3ZxVGNsNTZ1U19hLTdTbEdvaXlyeGlnMjZGODZGbV9vNzVnb0pqQkEwNGk2cFZyN01SSGNvV2h1LUE?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,38 +1739,38 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46139.48428240741</v>
+        <v>46139.55391203704</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>La guerre ouverte entre narcotrafiquants reprend de plus belle à Bruxelles - Virgule.lu</t>
+          <t>European travel demand hits highest level since 2020, but 90% stay within Europe - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The open war between drug traffickers resumes with a vengeance in Brussels - Virgule.lu</t>
+          <t>European travel demand hits highest level since 2020, but 90% stay within Europe - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 09:02:00 GMT</t>
+          <t>Mon, 27 Apr 2026 11:12:15 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNcWd1bVZNU1NHUm1aa0pISXZaLXQ0azN0dEs2ajVGWlk0UVpoZV8zakpwRWVDVFotTmk4Nkgwdm5vNEF0cmZTMUx3S01YaE5tSWVwTTI1b2g0Wl9ySW8xT1RTajlYalo3emxZa0R1VFZZNVhnQTd1WTluWnNzcVlyWXEzR3NsWEFOaVJGUVVNWWZua0swTXVKSnl2UTJMNzExZ2JBeERzaWp3aFdJd3RRbkRQVEVrWUVTWmd4SlgzT05JaFZz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNWTN5WmZSR1dkaUVjVTBWRlFrbXFHNjAtdnAxWUNoRjVWM3B5M0Z0R2stSk83UnBRU2FJWUF2cF9uWXZMekcwb21LTFBNTzJLR0lNMDlBdFg2R2I4YmJyamtOSGxTcTFFeGhNcUdVT3FYRENCM2ROVmFOVFpuQUZJQUM1V0wzWUl6LWVfS0xkR0haU3Z2aV85cnRCOWpmeHdxZ2JGZUVsbUMtUQ?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1790,42 +1790,42 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46139.37638888889</v>
+        <v>46139.46684027778</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DS en français Chaque jour, une sélection d’articles pertinents dans une édition numérique innovante - De Standaard</t>
+          <t>Outdated rail systems make European train travel harder than flying - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DS in French Every day, a selection of relevant articles in an innovative digital edition - De Standaard</t>
+          <t>Outdated rail systems make European train travel harder than flying - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:13:24 GMT</t>
+          <t>Mon, 27 Apr 2026 11:37:22 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxONGJubW1mM1VLdWZRc3V6UWZ3WEVZSjI5WUkwX1VjblRkOUlRUmlhLXpIbE41cVhaLXZUY1J5azAwR2lmM1cxNDhSLVFfQTU2ckxWcmpSd1VDSDNhZXZqWExUbVVidmpHdWtyZWljbURpdFJVWGxCUERUOC1uLUlQbWQ5YmREbGFTdWw0N0FCcThpRVV6bXJPd1BR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNNHZoc1NHNHBPeDRPRm1GY1JkRE5zWWRneXJTUkhKWHRMOUdJZlRJNFJTVF9mOXZIN2ZhNk9lWFljUUM0UVpxZ3FxOWIwTGxtSUlaWm1tVk9TckNFcWRJdG9YVE5CRUhRaGJka2h5RERzdUNxcW5RSU5kSDhzU3JleENLY2d6cE5EVUhLRC1SYUhYNjFQOHpVNDVLZw?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1845,42 +1845,42 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46139.30097222222</v>
+        <v>46139.48428240741</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Demande d'extradition pour l'homme interpellé à Maastricht après une course-poursuite - DHnet</t>
+          <t>La guerre ouverte entre narcotrafiquants reprend de plus belle à Bruxelles - Virgule.lu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Extradition request for man arrested in Maastricht after chase - DHnet</t>
+          <t>The open war between drug traffickers resumes with a vengeance in Brussels - Virgule.lu</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 12:45:00 GMT</t>
+          <t>Mon, 27 Apr 2026 09:02:00 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNN0VSR2I5c2huY3RPZ2pqRzdVZW1YWVJPZlkwN2Q0YUpFaDQ2emxtam11NHVTR3RndEVQbmM1Q0RyNlRIb2xvRXdKQUJtbTBVZWYyWnZUTjF0Y1BCcVA3WGNtWHZRNjY3TWwzY2NtZ0FreVZubFBIMV9CLTdXeTQ2a1lvTF95ZGtEZFR0cHlwZW0wNndxTVhRRkZvY19RbG5NYUJYMXpJYWsxTFRHU3pmbzdWdGdEMnQ0Ri1KbDdPN19rWEpTQzVBWDU5V2tBckRFSzRNU3lxYmxaMWtYTVFvSVJYaUpIMTZhVFZ2c0VrOHMtSmhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNcWd1bVZNU1NHUm1aa0pISXZaLXQ0azN0dEs2ajVGWlk0UVpoZV8zakpwRWVDVFotTmk4Nkgwdm5vNEF0cmZTMUx3S01YaE5tSWVwTTI1b2g0Wl9ySW8xT1RTajlYalo3emxZa0R1VFZZNVhnQTd1WTluWnNzcVlyWXEzR3NsWEFOaVJGUVVNWWZua0swTXVKSnl2UTJMNzExZ2JBeERzaWp3aFdJd3RRbkRQVEVrWUVTWmd4SlgzT05JaFZz?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1904,38 +1904,38 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46139.53125</v>
+        <v>46139.37638888889</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tenns club serves up a membership fee shock - North Norfolk News</t>
+          <t>Trois employés de la prison de Haren agressés vendredi dernier - BruxellesToday</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tenns club serves up a membership fee shock - North Norfolk News</t>
+          <t>Three Haren prison employees attacked last Friday - BruxellesToday</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 10:05:00 GMT</t>
+          <t>Mon, 27 Apr 2026 11:32:00 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQWXZHRXZ5YUdqQzlndXd2Wm5tZ0tma29kenZIVjNvYkZ6d2JrOTRfSHVWVkdDZ1RCVTlIczQ2UHBfZkhVZG80UkM1V3VOck12T2ZpRVlVTkhFOGx3dkducXgtQXRuSkVyNEJwT2t3cTlBbS1yLUhsZmpXbEtTbXRJMUJvSkRIakx2bERQd3RSbjJjdmlKRlBiYnFiWkxaZkJfcmtnN2xB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbmJpa3pRZWFsR2tDZmVUZkpldHRCbDUzLU9aM2dxV1R0ZVpiQ1VHVkNOVDVxZDNtcU1YOU02MG5RNkpoYWhkNVRIMXp0NXBZVzR4VDBRNkxzaGxKc2pfTFVVdFdSTXRBbGlCdjdjVGJPVUJjcVJsVENhb0hsV1VOVllXTFQyMmc?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1945,52 +1945,52 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46139.42013888889</v>
+        <v>46139.48055555556</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Polizei- und Feuerwehrmeldungen am 27.04.2026 aus Bayern - Newsflash24</t>
+          <t>Demande d'extradition pour l'homme interpellé à Maastricht après une course-poursuite - DHnet</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Police and fire brigade reports from Bavaria on April 27, 2026 - Newsflash24</t>
+          <t>Extradition request for man arrested in Maastricht after chase - DHnet</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 06:53:00 GMT</t>
+          <t>Mon, 27 Apr 2026 12:45:00 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZWRQWTdjSUw4VnNNdlRaWkpnem85WXlDdzZQcHEySWh5WGdGYWY5MWwxbXNXMXp2NGNIbTI3dDhPOWpOaGdvZkRwQTR0SEFJTGdkbjhHVlltYTc4cVpOQm14ZWMxSlM5XzhoQVdVUXRpYjN6ODRCTGJGZ1hIUHdNamNDNktVMHBIeE81UWR6Vm4tS3FYSUVFVXZnb0s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNN0VSR2I5c2huY3RPZ2pqRzdVZW1YWVJPZlkwN2Q0YUpFaDQ2emxtam11NHVTR3RndEVQbmM1Q0RyNlRIb2xvRXdKQUJtbTBVZWYyWnZUTjF0Y1BCcVA3WGNtWHZRNjY3TWwzY2NtZ0FreVZubFBIMV9CLTdXeTQ2a1lvTF95ZGtEZFR0cHlwZW0wNndxTVhRRkZvY19RbG5NYUJYMXpJYWsxTFRHU3pmbzdWdGdEMnQ0Ri1KbDdPN19rWEpTQzVBWDU5V2tBckRFSzRNU3lxYmxaMWtYTVFvSVJYaUpIMTZhVFZ2c0VrOHMtSmhn?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2000,52 +2000,52 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46139.28680555556</v>
+        <v>46139.53125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>Local Town Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Why Germany's Auto Capitals — Stuttgart, Munich, Wolfsburg — Are Facing a Financial Crisis That's Deeper Than the Headlines Show - primaryignition.com</t>
+          <t>Tenns club serves up a membership fee shock - EDP24</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Why Germany's Auto Capitals — Stuttgart, Munich, Wolfsburg — Are Facing a Financial Crisis That's Deeper Than the Headlines Show - primaryignition.com</t>
+          <t>Tenns club serves up a membership fee shock - EDP24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 09:04:15 GMT</t>
+          <t>Mon, 27 Apr 2026 10:05:00 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOVi1Yal9yNGJYaklBT2N1XzYwdDFXc0VpOWowV2hDRkxNNFN3Tl8xbDRxcUxJdm9lNkpKTmdad1dVLWNQWVd4QThBaEk0UjNwTjJxZjFwSm9ocHBHVDhNLUtxb1ozUlBJMEJCOUV3R3JNV3pPNHk0NEpsUlZEWG5mNzZma3Y4SzRGeVM2ZkloaV8xRVhiWEcxQzg5Z19mbWZFUmg2Ukt2UmtXUUNkemI4RFduZkVYWTZQNVpNQk1WOGw2YTItY3RMVUl1NzlTQWo5S3I0c1VqYlVMQ2plN19vdDFFRVB3VkhSNW9ib0IzX3BkQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNMW1CMHpveEZXYjZsYkFXcHA2bVFhLXVZZ1hpSklEdDlSMFJFVVcyRUtfY19pTzZiVTFhVGRTN01WSkpBd3RLRS04aUJnLWlrSTdFVURSVXpsQjdZUUhicGNVUkNlWjFqTXNQcUdpRmtEZXNTQXEzY0xKWlpxbkRUT0VpNEMyRmZvcEpqMUpfSnI5R09WWW00?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,38 +2069,38 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46139.37795138889</v>
+        <v>46139.42013888889</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Village Las Rozas La Roca (fallback)</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Las Rozas Village" OR "La Roca Village" OR "Las Rozas" OR "La Roca") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>All Costco stores to close for 24 hours this week as shoppers make other plans - MSN</t>
+          <t>Audi Is Replacing Its Smallest Models With A New Electric Gateway - Yahoo Autos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>All Costco stores to close for 24 hours this week as shoppers make other plans - MSN</t>
+          <t>Audi Is Replacing Its Smallest Models With A New Electric Gateway - Yahoo Autos</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 06:56:15 GMT</t>
+          <t>Mon, 27 Apr 2026 14:30:09 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigANBVV95cUxQSkZsa18zRU11SUdtNEI0MnY1OXc5aEtwWnl2Tmh6VGJvSTNtLWpMMEdNNTQ0c0NnM0JJSDkxall3Zzc5U0hZMGZsTlAzTHRBc21RSzJXNVVyVV9GMVl5bUw5QXVHU002a0hEY2xxc3BQdHRzdzN5NWdLNWU1OWVNMDRTMTBiM0lRZEVTalU2M0pfSmJpMUFyVmR0TjExT1FiVjlNVUQ4NjJ2NUFNX01BdF9IYWM2S3N2UHVkMEFjb1RTeEhidFYxOW1jU18xS3V1cEhiSkZhX2IwMzQ3S082Sm1ObVEtWGlCS1dkTm1oOUVsT2hudkg2TENXaGtLT3hvT1RtZmFXX2FSSjdiMkw2VnFnaGc1V1JFdXY4S3hBTHdrYWtKeExMaG1JWEk4LXZ0djB5Yi1yMzlNeC1URE43d29JcGtTdWs4MTNqanZMSjJRMFIxRWNUNXZ2LThZN2x4R21vVjJGczczVmxDWDBWeDZSaUhhS2dZNE1Lc2pUTWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxORjZxemZvVG1Senl0Q29xdG9uZllPazBBSmJXTjlPNlF1NWYzUS1MZG05dmd2OUpYVjlkLTNZcVMwVkNvdjZKbTJlc19tS3VFYVUwb0xzRzNUbVF6QlVzUlR6WGlUYUEwbUFBTFlXYXREaExqLTZrQWtNMl94RksxTXNxdllqN1RESXNXcGdUUno5WU9rd09WaEQySFBPcWQ4eUxtQ1cydEhRUQ?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,38 +2124,38 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46139.2890625</v>
+        <v>46139.60427083333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Man admits stabbing landlord and 14-year-old in Uxbridge - BBC</t>
+          <t>Why Germany's Auto Capitals — Stuttgart, Munich, Wolfsburg — Are Facing a Financial Crisis That's Deeper Than the Headlines Show - primaryignition.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Man admits stabbing landlord and 14-year-old in Uxbridge - BBC</t>
+          <t>Why Germany's Auto Capitals — Stuttgart, Munich, Wolfsburg — Are Facing a Financial Crisis That's Deeper Than the Headlines Show - primaryignition.com</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 11:02:24 GMT</t>
+          <t>Mon, 27 Apr 2026 09:04:15 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBXd3VQRTMzQ3JnUFdsVkx5RzBYYlpkS3N0SmlONXc3WF9yZTJUNHF0Y3NvNTZnNnBPLTNiZzRiRnN6SExpU1pHRGdlc25yRFJ6Y3p0dU1uM2JsaFRs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOVi1Yal9yNGJYaklBT2N1XzYwdDFXc0VpOWowV2hDRkxNNFN3Tl8xbDRxcUxJdm9lNkpKTmdad1dVLWNQWVd4QThBaEk0UjNwTjJxZjFwSm9ocHBHVDhNLUtxb1ozUlBJMEJCOUV3R3JNV3pPNHk0NEpsUlZEWG5mNzZma3Y4SzRGeVM2ZkloaV8xRVhiWEcxQzg5Z19mbWZFUmg2Ukt2UmtXUUNkemI4RFduZkVYWTZQNVpNQk1WOGw2YTItY3RMVUl1NzlTQWo5S3I0c1VqYlVMQ2plN19vdDFFRVB3VkhSNW9ib0IzX3BkQQ?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46139.46</v>
+        <v>46139.37795138889</v>
       </c>
     </row>
     <row r="33">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
+          <t>Man admits stabbing landlord and 14-year-old in Uxbridge - BBC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
+          <t>Man admits stabbing landlord and 14-year-old in Uxbridge - BBC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 13:36:26 GMT</t>
+          <t>Mon, 27 Apr 2026 11:02:24 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPQmVxTDFaRG0xYnJMZGdpekE5R0ZOd2hEX2FxZlpKVGpQNE9scDdpYnA0UXJISjY0Qmh4YlZsOE1uMXIya1ZZZDNQRUlYZDVGX256RndxVENaWDJXT095NVc4MHEyYWVCek9kcjFpV2Y5VF9nSVBHcG83RlE3U3gxWnY2clk1czVGX1dtUzE1a0VtekNiYzZF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBXd3VQRTMzQ3JnUFdsVkx5RzBYYlpkS3N0SmlONXc3WF9yZTJUNHF0Y3NvNTZnNnBPLTNiZzRiRnN6SExpU1pHRGdlc25yRFJ6Y3p0dU1uM2JsaFRs?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46139.56696759259</v>
+        <v>46139.46</v>
       </c>
     </row>
     <row r="34">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>London fuel tax protest LIVE: Demonstrators set to gather in Whitehall for Reform-organised 'national rally' - AOL.com</t>
+          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>London fuel tax protest LIVE: Demonstrators set to gather in Whitehall for Reform-organised 'national rally' - AOL.com</t>
+          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 08:20:26 GMT</t>
+          <t>Mon, 27 Apr 2026 13:36:26 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5FWGplRGFSMUFjTTJsRElIeUt1Z3RfUVJvaEtZNVFMRkdJbUpYR2xLQldaX3hYbGI1X3BKY3FnUnpHWHpZdGZmT2J1eGNpOUNhT25WNnN3VVRscG9RVUhlTHZKd0NEY2RWbGM5d3N1LUZINUduX3N3QkpIVUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPQmVxTDFaRG0xYnJMZGdpekE5R0ZOd2hEX2FxZlpKVGpQNE9scDdpYnA0UXJISjY0Qmh4YlZsOE1uMXIya1ZZZDNQRUlYZDVGX256RndxVENaWDJXT095NVc4MHEyYWVCek9kcjFpV2Y5VF9nSVBHcG83RlE3U3gxWnY2clk1czVGX1dtUzE1a0VtekNiYzZF?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46139.34752314815</v>
+        <v>46139.56696759259</v>
       </c>
     </row>
     <row r="35">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leyton fatal stabbing victim named and pictured as police charge two men with murder - My London</t>
+          <t>Boy, 17, left with potentially life changing injuries after stabbing in Westminster - London Now</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Leyton fatal stabbing victim named and pictured as police charge two men with murder - My London</t>
+          <t>Boy, 17, left with potentially life changing injuries after stabbing in Westminster - London Now</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 06:59:10 GMT</t>
+          <t>Mon, 27 Apr 2026 14:13:58 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNZjBlVjRzTlgzNUZsbFUzZkdST3lZb0EyazZLNVRwSkd6MmNncFoxRVlHZlFxOHRIVzVYVTk1QUpkTTJaNGRjX1Z0cVRZajJLT1hlOTllcGVud3p6LUcyRUFpX2R5elMwSWMyaWVJeHhRT0pSZFA2eXdRX0RlYkhvcldWZjMwTknSAYwBQVVfeXFMTW0zcmFyaHVMNTQ1RHFja3ZDVE91Mms1QlJRYnJYRnh6N3pBVEd5MzE0Q2pGcGVrYjRfZTVsNmFfM1RmVG55VmdGSFdYQXl6bVNwSkVFbzZyd292MS04SElpeXdLVmNDbVA0elNYbjFLVnZROURveEZrQmpTSHlaUzZIMEJHdVN6a1JlbXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOa0lCZU5CNmNXQ2V6YVRZaUlfaXdaOE5YXzd0UmV2YWM5X2dLZ29rRWhMVl9CN2wwZzlQUENyS1BfcEN0VFZfWDVacmVNWkdWVU1XUlVjVlhTcVFldXBWMFhQcHJQVjZDNUNVd2RyZm9zQXBobDZBN2Y2dmxwd0hyaGlBaU5yT3ZrR3U1dFlkNXBPdlFNRDNzYlpJS2hwY2M?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46139.29108796296</v>
+        <v>46139.59303240741</v>
       </c>
     </row>
     <row r="36">
@@ -2360,22 +2360,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sixth form 'gave first aid to stabbed boy, 17,' after parent found him injured - London Now</t>
+          <t>London fuel tax protest LIVE: Demonstrators set to gather in Whitehall for Reform-organised 'national rally' - AOL.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sixth form 'gave first aid to stabbed boy, 17,' after parent found him injured - London Now</t>
+          <t>London fuel tax protest LIVE: Demonstrators set to gather in Whitehall for Reform-organised 'national rally' - AOL.com</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 11:17:25 GMT</t>
+          <t>Mon, 27 Apr 2026 08:20:26 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQeVlDTFU2SnE0SncwZDk5SGhmWEhBNFFLWHNSUl9pei1mREJQMHZEbU5PajhYZVJLcXpJV0hlblFkNm1LUmdxYUwyb2NfNDZ6X1FWZnlaekY1VFJOeTI3SWh3cXdScGRGRWVOcmZXUkNSRktEMGVGejlCcDhENGNhU04zMkE0cjl1U25RMEdaUFdPMkJLYXZTdUxzQWM3aFFw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5FWGplRGFSMUFjTTJsRElIeUt1Z3RfUVJvaEtZNVFMRkdJbUpYR2xLQldaX3hYbGI1X3BKY3FnUnpHWHpZdGZmT2J1eGNpOUNhT25WNnN3VVRscG9RVUhlTHZKd0NEY2RWbGM5d3N1LUZINUduX3N3QkpIVUQ?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46139.47042824074</v>
+        <v>46139.34752314815</v>
       </c>
     </row>
     <row r="37">
@@ -2470,22 +2470,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Large crowds pay tribute to 'loving' man, 21, stabbed to death in Primrose Hill - London Now</t>
+          <t>Reform UK protest draws just two vehicles despite calls for mass turnout - London Now</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Large crowds pay tribute to 'loving' man, 21, stabbed to death in Primrose Hill - London Now</t>
+          <t>Reform UK protest draws just two vehicles despite calls for mass turnout - London Now</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 08:54:04 GMT</t>
+          <t>Mon, 27 Apr 2026 13:59:33 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQT2tLV0VlLXRDMS1CWmNaMXZVRENGbUpWNUM4UlVyUDhZNWlJRWR5RzAySkVEVkxZQzloQ0MxNGdqUlZPeTVfamV5S2NVVUwwUWRFUHNVY05tUjNYNDJXVWZmdENTM0Z1S2VmZXg5Z2wtc3NIS3BCM3c4N3JDVlhEbVE4ei04LUY4eUNxYVAxUEtZRmRyRno3QXI0MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOWTNMLVJ6T0tZSU5NQ2VteDRJUmJRTTdqVURPRHBTMzd6eWZINHRMbVhwMUNKMUl1MEt3aUxEN3BrcUpVTXdOQ3RJdDd2ak5kYXpyYWlybzRtQnZfcjdGZFBibEhsQjQzSXJNd0owLXFzS29vRU0tOXVXNmpNUzlRYlpfTFVFY3hwX3VncHhzQ0k0WWs?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46139.37087962963</v>
+        <v>46139.58302083334</v>
       </c>
     </row>
     <row r="39">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Children’s Rights Over Flights Protest Dublin Airport’s Passenger Cap - The University Times</t>
+          <t>Large crowds pay tribute to 'loving' man, 21, stabbed to death in Primrose Hill - London Now</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Children’s Rights Over Flights Protest Dublin Airport’s Passenger Cap - The University Times</t>
+          <t>Large crowds pay tribute to 'loving' man, 21, stabbed to death in Primrose Hill - London Now</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 13:16:40 GMT</t>
+          <t>Mon, 27 Apr 2026 08:54:04 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOMXlfVl83U2RwZzFqb2xnQmZsUEJENW82amNubDNJVE40NC11TURHcWpGMS1ycFJCb2UzVDRqZjk5X01aZ1dSVUZjNTFhdzdmOEx3UzBISWh4UzFnMFp5YXUwTkh2clNwYXZ1ejN0ekZJa0U0b0ZLSnVaZE9lNnQ0VjI0OFQyT2IxekpZcmZNYXhrZFllTDVPd1BPRmVyWWFERnozcEtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQT2tLV0VlLXRDMS1CWmNaMXZVRENGbUpWNUM4UlVyUDhZNWlJRWR5RzAySkVEVkxZQzloQ0MxNGdqUlZPeTVfamV5S2NVVUwwUWRFUHNVY05tUjNYNDJXVWZmdENTM0Z1S2VmZXg5Z2wtc3NIS3BCM3c4N3JDVlhEbVE4ei04LUY4eUNxYVAxUEtZRmRyRno3QXI0MA?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46139.55324074074</v>
+        <v>46139.37087962963</v>
       </c>
     </row>
     <row r="41">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>‘The Edge of Revolution’, ‘Britain’s Revolutionary Summer’ and ‘Nine Days in May’ review - History Today</t>
+          <t>Children’s Rights Over Flights Protest Dublin Airport’s Passenger Cap - The University Times</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>‘The Edge of Revolution’, ‘Britain’s Revolutionary Summer’ and ‘Nine Days in May’ review - History Today</t>
+          <t>Children’s Rights Over Flights Protest Dublin Airport’s Passenger Cap - The University Times</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:43:20 GMT</t>
+          <t>Mon, 27 Apr 2026 13:16:40 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNcG9PeFpiSXl6OC13N1dMUENBaHIwWHBsTG5EN3VZVE1YbWtFZFJzVFVOYV9KWV9wQ2dDdUFMYVNwV0p3NEpNU1E3dHRKZEd2UEZHdmg4U0c2WHdsWURJc09lSlgwcjR5ci0xclUxZlZCT2MxYmZHYzVfQUttcmpTQlNzVzZIUnBBNUpEM0FRanBRaTRuOHRWRDI1ZXdvTmlpS082UnhMQjlscjUyT0laTVE3NnU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOMXlfVl83U2RwZzFqb2xnQmZsUEJENW82amNubDNJVE40NC11TURHcWpGMS1ycFJCb2UzVDRqZjk5X01aZ1dSVUZjNTFhdzdmOEx3UzBISWh4UzFnMFp5YXUwTkh2clNwYXZ1ejN0ekZJa0U0b0ZLSnVaZE9lNnQ0VjI0OFQyT2IxekpZcmZNYXhrZFllTDVPd1BPRmVyWWFERnozcEtR?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2674,38 +2674,38 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46139.32175925926</v>
+        <v>46139.55324074074</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City Italy English</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND ("minaccia bomba" OR "pacco sospetto" OR "pacco esplosivo" OR sparatoria OR accoltellamento OR "attentato" OR "operazione di polizia" OR esplosione OR evacuazione) AND -Olimpiadi AND -pattinaggio AND -sci AND -Cortina AND -calcio AND -Serie AND -mercato</t>
+          <t>("Milan" OR "Milano" OR "Bologna") AND ("Italy" OR "Italian") AND (protest OR demonstration OR rally OR "civil unrest" OR strike OR blockade OR march) AND -football AND -transfer AND -Serie AND -"fashion week" AND -catwalk AND -runway</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Aggressione a Milano, 14enne accoltellato alla schiena e alla testa: è grave - Adnkronos</t>
+          <t>Jewish community harassed and expelled from Milan’s Liberation Day parade - The Jerusalem Post</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Attack in Milan, 14 year old stabbed in the back and head: it's serious - Adnkronos</t>
+          <t>Jewish community harassed and expelled from Milan’s Liberation Day parade - The Jerusalem Post</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:28:00 GMT</t>
+          <t>Mon, 27 Apr 2026 10:54:24 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNWWZfbF9JNnptb2QteEVBeExCdy1YX2ZPMWwtZVhvLXMxOHRSNlc1TkZkc21NNjJBM2EwS1Z4eW96MVlVTnZrazMzbm9NXzBqU2J5THNScG1Na0NESXBORTVBSUFNX3FHeFp1b3Zyejd4YzJobEhreDVvT2ZDZEJLR1ZCMDhlQnhEWG8yUjZpYzM3U2I1RTlCblpJektJT3kx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE05LUhTSjJaTFJIRWpRUVlzQXd1TWZXSmhNYTNLYU41cFBpNTI0bm1rRzMxaEl1UjJxR1hla0tZREtPaUZxSW1wSVp5My1oOFJwajVmOWc5aUtKT19qNHFiRkdva1lOU3VDVkE?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2725,42 +2725,42 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>IT:en</t>
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46139.31111111111</v>
+        <v>46139.45444444445</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City Italy English</t>
+          <t>Hate Crime Europe English</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Milan" OR "Milano" OR "Bologna") AND ("Italy" OR "Italian") AND (protest OR demonstration OR rally OR "civil unrest" OR strike OR blockade OR march) AND -football AND -transfer AND -Serie AND -"fashion week" AND -catwalk AND -runway</t>
+          <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jewish community harassed and expelled from Milan’s Liberation Day parade - The Jerusalem Post</t>
+          <t>UK police arrest man for terror plot in probe of antisemitic attacks - The Times of Israel</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jewish community harassed and expelled from Milan’s Liberation Day parade - The Jerusalem Post</t>
+          <t>UK police arrest man for terror plot in probe of antisemitic attacks - The Times of Israel</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 10:54:24 GMT</t>
+          <t>Mon, 27 Apr 2026 08:51:49 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE05LUhTSjJaTFJIRWpRUVlzQXd1TWZXSmhNYTNLYU41cFBpNTI0bm1rRzMxaEl1UjJxR1hla0tZREtPaUZxSW1wSVp5My1oOFJwajVmOWc5aUtKT19qNHFiRkdva1lOU3VDVkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOXJfLTdSNjVpenZGakpkYWpRdkJmb2hWemVqTjdaZHo3RXprbFk2M0FHVWt0eGUyb1Fhd3A2T2x4NFV5WVI0R1dpcXUwLVVsSXlneGg5M1UzUkJwdFF6TmRrNWFqeW0tOHlEUXZxbl96SEZ3UjVpWlVCQnRLNjAtUVFkaVJjRUtQaGVaZ2tFY0o4MVBjQWx3akpsNEtQTW9Q0gGmAUFVX3lxTE5UcHZ5TlJhcC1qaHI4MmNIU3pndW44d29xYTF5NFlEUktoV2hncG9HNThTYzNfLUFTLV9Bb3pVaVVEREpkaVBXa0xfRG9IcUN6N0FuSGlTdDVheGpHTk5ZNk5EYVYySW1mUW53bHR3elRJMjBXajdWX3JITXdNMnBVQWhKVk5fdXhBOHVzaUowdHJkVzVXZGk5emVqODhYRDFtMFdwYUE?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2775,47 +2775,47 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>IT:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46139.45444444445</v>
+        <v>46139.36931712963</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>Spain Transport Disruption Spanish</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Cercanías" OR "Renfe" OR "Metro Madrid" OR "Metro Barcelona" OR "AVE" OR "autopista" OR "autovía" OR "A6" OR "M40" OR "M30" OR "M50") AND ("amenaza de bomba" OR "paquete sospechoso" OR evacuación OR suspensión OR corte OR incidente OR "orden público" OR detenido OR explosivo OR desalojo) AND ("Madrid" OR "Barcelona" OR "Las Rozas" OR "Pozuelo")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brigata ebraica, foto di Trump, bandiere di Israele e Scià: perché il 25 aprile è scoppiato il caos - MilanoToday</t>
+          <t>Una falsa amenaza de bomba obliga a desalojar un tren de Cercanías en Pozuelo de Alarcón - ABC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jewish brigade, photos of Trump, flags of Israel and the Shah: why chaos broke out on April 25 - MilanoToday</t>
+          <t>A false bomb threat forces the evacuation of a Cercanías train in Pozuelo de Alarcón - ABC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:37:42 GMT</t>
+          <t>Mon, 27 Apr 2026 10:25:01 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOQTdhX0FGeGg1YW81Z01HZTZYeFpyeUVtX0R1a3BPUnF3RWd0dnBxZXlYX3dtTUNFZFB3Zm1DZWUzc3ZreEQ1WFRHN0Rfa05Oa2lZUzlUQ3kwd2xHeGhIRXhsN1lwanhWX092Z1p6TnNkWmFPemFheGxxYVF5UVdBdkpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPTllRWnZNVzdYRy0zX21PQXlST3ZualQyemdDUlVXRDFRcnJ6Q2xjMXVVaUJxY1JQSVFaWU5PdGlSUmtId0c3c1c1TndrSEE1cXk2ZlFZQmwxbTVYYzFrVGs2Zk5sRzZtaVFfRlNzcUZiLUV0LVVRUnY4MkcwTnhUd093cy1lMnVKR2FEYjlxQWVERkkxaUJqZFJXMXRuRUhQaTdQZzA1X0JBVlU?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2825,52 +2825,52 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>es</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46139.31784722222</v>
+        <v>46139.43403935185</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hate Crime Europe English</t>
+          <t>Spain Transport Disruption Spanish</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
+          <t>("Cercanías" OR "Renfe" OR "Metro Madrid" OR "Metro Barcelona" OR "AVE" OR "autopista" OR "autovía" OR "A6" OR "M40" OR "M30" OR "M50") AND ("amenaza de bomba" OR "paquete sospechoso" OR evacuación OR suspensión OR corte OR incidente OR "orden público" OR detenido OR explosivo OR desalojo) AND ("Madrid" OR "Barcelona" OR "Las Rozas" OR "Pozuelo")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UK police arrest man for terror plot in probe of antisemitic attacks - The Times of Israel</t>
+          <t>Desalojan un tren y cortan el servicio de Cercanías Madrid por una falsa amenaza de bomba en El Barrial - MiraCorredor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UK police arrest man for terror plot in probe of antisemitic attacks - The Times of Israel</t>
+          <t>They evacuate a train and cut the Cercanías Madrid service due to a false bomb threat in El Barrial - MiraCorredor</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 08:51:49 GMT</t>
+          <t>Mon, 27 Apr 2026 10:28:16 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOXJfLTdSNjVpenZGakpkYWpRdkJmb2hWemVqTjdaZHo3RXprbFk2M0FHVWt0eGUyb1Fhd3A2T2x4NFV5WVI0R1dpcXUwLVVsSXlneGg5M1UzUkJwdFF6TmRrNWFqeW0tOHlEUXZxbl96SEZ3UjVpWlVCQnRLNjAtUVFkaVJjRUtQaGVaZ2tFY0o4MVBjQWx3akpsNEtQTW9Q0gGmAUFVX3lxTE5UcHZ5TlJhcC1qaHI4MmNIU3pndW44d29xYTF5NFlEUktoV2hncG9HNThTYzNfLUFTLV9Bb3pVaVVEREpkaVBXa0xfRG9IcUN6N0FuSGlTdDVheGpHTk5ZNk5EYVYySW1mUW53bHR3elRJMjBXajdWX3JITXdNMnBVQWhKVk5fdXhBOHVzaUowdHJkVzVXZGk5emVqODhYRDFtMFdwYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPdUliMEdoSUhhMkFaa0FzMURkQWtEQ2dmTkZoRE5Qb3dXYVhzQm4xNVpDbTFtY0g2bjdMUm5YRmlyYkpwc2dUUEtGX3F1X3YwZm9JWG9NRktpZ3R4TGFCb2sxc1dWb2I2UnNDb2JBMzZNa01iOWVRdXZiaENPbHk1NTFIRXhjSkJJYWQ5Q29zd2pmd2lzRkF2YXk3SnZhUjNmS2lwMjl4Y0pBcVpGOVh5UXJYS2dkUGlPbUg0VTV3WHVmWHJxTmtWNl9FX1U0VF9kbU9RM0FTQm8yaXRueGc?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2880,21 +2880,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>es</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46139.36931712963</v>
+        <v>46139.4362962963</v>
       </c>
     </row>
   </sheetData>
